--- a/config/永泰_2_BCU.xlsx
+++ b/config/永泰_2_BCU.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="报文" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="138">
   <si>
     <t>序号</t>
   </si>
@@ -443,18 +443,6 @@
   </si>
   <si>
     <t>单元素BitLen</t>
-  </si>
-  <si>
-    <t>单体电压</t>
-  </si>
-  <si>
-    <t>cell_voltage</t>
-  </si>
-  <si>
-    <t>0x1C0030D0</t>
-  </si>
-  <si>
-    <t>0xFFFF</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1094,9 +1082,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2258,7 +2243,7 @@
     <col min="5" max="6" width="9.11111111111111" style="2"/>
     <col min="7" max="7" width="11.7936507936508" style="2" customWidth="1"/>
     <col min="8" max="12" width="9.11111111111111" style="2"/>
-    <col min="13" max="13" width="21.6031746031746" style="4" customWidth="1"/>
+    <col min="13" max="13" width="21.6031746031746" style="3" customWidth="1"/>
     <col min="14" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
@@ -2299,7 +2284,7 @@
       <c r="L1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>59</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -2313,7 +2298,7 @@
       <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2">
@@ -2345,7 +2330,7 @@
       <c r="B3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="2">
@@ -2377,7 +2362,7 @@
       <c r="B4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2">
@@ -2409,7 +2394,7 @@
       <c r="B5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="2">
@@ -3753,7 +3738,7 @@
       <c r="B47" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E47" s="2">
@@ -3785,7 +3770,7 @@
       <c r="B48" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E48" s="2">
@@ -3817,7 +3802,7 @@
       <c r="B49" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E49" s="2">
@@ -3858,19 +3843,19 @@
       <c r="F50" s="2">
         <v>2</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I50" s="6">
+      <c r="G50" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I50" s="5">
         <v>0.1</v>
       </c>
-      <c r="J50" s="6">
-        <v>0</v>
-      </c>
-      <c r="K50" s="6" t="s">
+      <c r="J50" s="5">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3890,19 +3875,19 @@
       <c r="F51" s="2">
         <v>2</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I51" s="6">
+      <c r="G51" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I51" s="5">
         <v>0.1</v>
       </c>
-      <c r="J51" s="6">
-        <v>0</v>
-      </c>
-      <c r="K51" s="6" t="s">
+      <c r="J51" s="5">
+        <v>0</v>
+      </c>
+      <c r="K51" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3922,19 +3907,19 @@
       <c r="F52" s="2">
         <v>2</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I52" s="6">
+      <c r="G52" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I52" s="5">
         <v>0.1</v>
       </c>
-      <c r="J52" s="6">
-        <v>0</v>
-      </c>
-      <c r="K52" s="6" t="s">
+      <c r="J52" s="5">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3954,19 +3939,19 @@
       <c r="F53" s="2">
         <v>2</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I53" s="6">
+      <c r="G53" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I53" s="5">
         <v>0.1</v>
       </c>
-      <c r="J53" s="6">
-        <v>0</v>
-      </c>
-      <c r="K53" s="6" t="s">
+      <c r="J53" s="5">
+        <v>0</v>
+      </c>
+      <c r="K53" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3986,19 +3971,19 @@
       <c r="F54" s="2">
         <v>2</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I54" s="6">
+      <c r="G54" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I54" s="5">
         <v>0.1</v>
       </c>
-      <c r="J54" s="6">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="s">
+      <c r="J54" s="5">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4009,7 +3994,7 @@
       <c r="B55" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="5" t="s">
         <v>43</v>
       </c>
       <c r="E55" s="2">
@@ -4018,19 +4003,19 @@
       <c r="F55" s="2">
         <v>2</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I55" s="6">
+      <c r="G55" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I55" s="5">
         <v>0.1</v>
       </c>
-      <c r="J55" s="6">
-        <v>0</v>
-      </c>
-      <c r="K55" s="6" t="s">
+      <c r="J55" s="5">
+        <v>0</v>
+      </c>
+      <c r="K55" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4050,19 +4035,19 @@
       <c r="F56" s="2">
         <v>2</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I56" s="6">
+      <c r="G56" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I56" s="5">
         <v>0.1</v>
       </c>
-      <c r="J56" s="6">
-        <v>0</v>
-      </c>
-      <c r="K56" s="6" t="s">
+      <c r="J56" s="5">
+        <v>0</v>
+      </c>
+      <c r="K56" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4082,19 +4067,19 @@
       <c r="F57" s="2">
         <v>2</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I57" s="6">
+      <c r="G57" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I57" s="5">
         <v>0.1</v>
       </c>
-      <c r="J57" s="6">
-        <v>0</v>
-      </c>
-      <c r="K57" s="6" t="s">
+      <c r="J57" s="5">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4114,19 +4099,19 @@
       <c r="F58" s="2">
         <v>2</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I58" s="6">
+      <c r="G58" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I58" s="5">
         <v>0.1</v>
       </c>
-      <c r="J58" s="6">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="s">
+      <c r="J58" s="5">
+        <v>0</v>
+      </c>
+      <c r="K58" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4137,7 +4122,7 @@
       <c r="B59" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E59" s="2">
@@ -4146,19 +4131,19 @@
       <c r="F59" s="2">
         <v>2</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I59" s="6">
+      <c r="G59" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I59" s="5">
         <v>0.1</v>
       </c>
-      <c r="J59" s="6">
-        <v>0</v>
-      </c>
-      <c r="K59" s="6" t="s">
+      <c r="J59" s="5">
+        <v>0</v>
+      </c>
+      <c r="K59" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4169,7 +4154,7 @@
       <c r="B60" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E60" s="2">
@@ -4178,19 +4163,19 @@
       <c r="F60" s="2">
         <v>2</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I60" s="6">
+      <c r="G60" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I60" s="5">
         <v>0.1</v>
       </c>
-      <c r="J60" s="6">
-        <v>0</v>
-      </c>
-      <c r="K60" s="6" t="s">
+      <c r="J60" s="5">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4201,7 +4186,7 @@
       <c r="B61" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E61" s="2">
@@ -4210,19 +4195,19 @@
       <c r="F61" s="2">
         <v>2</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I61" s="6">
+      <c r="G61" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I61" s="5">
         <v>0.1</v>
       </c>
-      <c r="J61" s="6">
-        <v>0</v>
-      </c>
-      <c r="K61" s="6" t="s">
+      <c r="J61" s="5">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4242,19 +4227,19 @@
       <c r="F62" s="2">
         <v>2</v>
       </c>
-      <c r="G62" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I62" s="6">
+      <c r="G62" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I62" s="5">
         <v>0.1</v>
       </c>
-      <c r="J62" s="6">
-        <v>0</v>
-      </c>
-      <c r="K62" s="6" t="s">
+      <c r="J62" s="5">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4265,7 +4250,7 @@
       <c r="B63" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="5" t="s">
         <v>47</v>
       </c>
       <c r="E63" s="2">
@@ -4274,19 +4259,19 @@
       <c r="F63" s="2">
         <v>2</v>
       </c>
-      <c r="G63" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I63" s="6">
+      <c r="G63" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I63" s="5">
         <v>0.1</v>
       </c>
-      <c r="J63" s="6">
-        <v>0</v>
-      </c>
-      <c r="K63" s="6" t="s">
+      <c r="J63" s="5">
+        <v>0</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4299,8 +4284,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="1"/>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="9.11111111111111" style="2"/>
     <col min="3" max="3" width="12.2460317460317" style="2" customWidth="1"/>
@@ -4367,56 +4352,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="36" spans="1:17">
-      <c r="A2" s="2">
-        <v>2002</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E2" s="2">
-        <v>104</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2">
-        <v>4</v>
-      </c>
-      <c r="H2" s="2">
-        <v>416</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>2</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0.001</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/config/永泰_2_BCU.xlsx
+++ b/config/永泰_2_BCU.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268" activeTab="2"/>
+    <workbookView windowWidth="18569" windowHeight="11268"/>
   </bookViews>
   <sheets>
     <sheet name="报文" sheetId="1" r:id="rId1"/>
@@ -2302,10 +2302,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>61</v>
@@ -2334,10 +2334,10 @@
         <v>13</v>
       </c>
       <c r="E3" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>61</v>
@@ -2366,10 +2366,10 @@
         <v>13</v>
       </c>
       <c r="E4" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>61</v>
@@ -2398,10 +2398,10 @@
         <v>13</v>
       </c>
       <c r="E5" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>61</v>
@@ -2430,10 +2430,10 @@
         <v>19</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>61</v>
@@ -2462,10 +2462,10 @@
         <v>19</v>
       </c>
       <c r="E7" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>61</v>
@@ -2494,10 +2494,10 @@
         <v>19</v>
       </c>
       <c r="E8" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F8" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>61</v>
@@ -2526,10 +2526,10 @@
         <v>19</v>
       </c>
       <c r="E9" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>61</v>
@@ -2558,10 +2558,10 @@
         <v>21</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>61</v>
@@ -2590,10 +2590,10 @@
         <v>21</v>
       </c>
       <c r="E11" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F11" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>61</v>
@@ -2622,10 +2622,10 @@
         <v>21</v>
       </c>
       <c r="E12" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>61</v>
@@ -2654,10 +2654,10 @@
         <v>21</v>
       </c>
       <c r="E13" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F13" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>61</v>
@@ -2686,10 +2686,10 @@
         <v>23</v>
       </c>
       <c r="E14" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F14" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>61</v>
@@ -2718,10 +2718,10 @@
         <v>23</v>
       </c>
       <c r="E15" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F15" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>61</v>
@@ -2750,10 +2750,10 @@
         <v>23</v>
       </c>
       <c r="E16" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F16" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>61</v>
@@ -2782,10 +2782,10 @@
         <v>23</v>
       </c>
       <c r="E17" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>61</v>
@@ -2814,10 +2814,10 @@
         <v>25</v>
       </c>
       <c r="E18" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>61</v>
@@ -2846,10 +2846,10 @@
         <v>25</v>
       </c>
       <c r="E19" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>61</v>
@@ -2878,10 +2878,10 @@
         <v>25</v>
       </c>
       <c r="E20" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>61</v>
@@ -2910,10 +2910,10 @@
         <v>25</v>
       </c>
       <c r="E21" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>61</v>
@@ -2942,10 +2942,10 @@
         <v>27</v>
       </c>
       <c r="E22" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>61</v>
@@ -2974,10 +2974,10 @@
         <v>27</v>
       </c>
       <c r="E23" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F23" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>61</v>
@@ -3006,10 +3006,10 @@
         <v>27</v>
       </c>
       <c r="E24" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F24" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>61</v>
@@ -3038,10 +3038,10 @@
         <v>27</v>
       </c>
       <c r="E25" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F25" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>61</v>
@@ -3070,10 +3070,10 @@
         <v>29</v>
       </c>
       <c r="E26" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F26" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>61</v>
@@ -3102,10 +3102,10 @@
         <v>29</v>
       </c>
       <c r="E27" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>61</v>
@@ -3134,10 +3134,10 @@
         <v>29</v>
       </c>
       <c r="E28" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>61</v>
@@ -3166,10 +3166,10 @@
         <v>29</v>
       </c>
       <c r="E29" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>61</v>
@@ -3198,10 +3198,10 @@
         <v>31</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>61</v>
@@ -3230,10 +3230,10 @@
         <v>31</v>
       </c>
       <c r="E31" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>61</v>
@@ -3262,10 +3262,10 @@
         <v>31</v>
       </c>
       <c r="E32" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F32" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>61</v>
@@ -3294,10 +3294,10 @@
         <v>31</v>
       </c>
       <c r="E33" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F33" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>61</v>
@@ -3326,10 +3326,10 @@
         <v>33</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F34" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>61</v>
@@ -3358,10 +3358,10 @@
         <v>33</v>
       </c>
       <c r="E35" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F35" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>61</v>
@@ -3390,10 +3390,10 @@
         <v>33</v>
       </c>
       <c r="E36" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F36" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>61</v>
@@ -3422,10 +3422,10 @@
         <v>33</v>
       </c>
       <c r="E37" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F37" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>61</v>
@@ -3454,10 +3454,10 @@
         <v>35</v>
       </c>
       <c r="E38" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F38" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>61</v>
@@ -3486,10 +3486,10 @@
         <v>35</v>
       </c>
       <c r="E39" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F39" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>61</v>
@@ -3518,10 +3518,10 @@
         <v>35</v>
       </c>
       <c r="E40" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>61</v>
@@ -3550,10 +3550,10 @@
         <v>35</v>
       </c>
       <c r="E41" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>61</v>
@@ -3582,10 +3582,10 @@
         <v>37</v>
       </c>
       <c r="E42" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F42" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>61</v>
@@ -3614,10 +3614,10 @@
         <v>37</v>
       </c>
       <c r="E43" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>61</v>
@@ -3646,10 +3646,10 @@
         <v>37</v>
       </c>
       <c r="E44" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F44" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>61</v>
@@ -3678,10 +3678,10 @@
         <v>37</v>
       </c>
       <c r="E45" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F45" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>61</v>
@@ -3710,10 +3710,10 @@
         <v>39</v>
       </c>
       <c r="E46" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F46" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>61</v>
@@ -3742,10 +3742,10 @@
         <v>39</v>
       </c>
       <c r="E47" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F47" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>61</v>
@@ -3774,10 +3774,10 @@
         <v>39</v>
       </c>
       <c r="E48" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F48" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>61</v>
@@ -3806,10 +3806,10 @@
         <v>39</v>
       </c>
       <c r="E49" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F49" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>61</v>
@@ -3838,10 +3838,10 @@
         <v>41</v>
       </c>
       <c r="E50" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F50" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>61</v>
@@ -3870,10 +3870,10 @@
         <v>41</v>
       </c>
       <c r="E51" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F51" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>61</v>
@@ -3902,10 +3902,10 @@
         <v>41</v>
       </c>
       <c r="E52" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F52" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>61</v>
@@ -3934,10 +3934,10 @@
         <v>41</v>
       </c>
       <c r="E53" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F53" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>61</v>
@@ -3966,10 +3966,10 @@
         <v>43</v>
       </c>
       <c r="E54" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F54" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>61</v>
@@ -3998,10 +3998,10 @@
         <v>43</v>
       </c>
       <c r="E55" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F55" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>61</v>
@@ -4030,10 +4030,10 @@
         <v>43</v>
       </c>
       <c r="E56" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F56" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>61</v>
@@ -4062,10 +4062,10 @@
         <v>43</v>
       </c>
       <c r="E57" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F57" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>61</v>
@@ -4094,10 +4094,10 @@
         <v>45</v>
       </c>
       <c r="E58" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F58" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>61</v>
@@ -4126,10 +4126,10 @@
         <v>45</v>
       </c>
       <c r="E59" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F59" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>61</v>
@@ -4158,10 +4158,10 @@
         <v>45</v>
       </c>
       <c r="E60" s="2">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F60" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>61</v>
@@ -4190,10 +4190,10 @@
         <v>45</v>
       </c>
       <c r="E61" s="2">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F61" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>61</v>
@@ -4222,10 +4222,10 @@
         <v>47</v>
       </c>
       <c r="E62" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F62" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>61</v>
@@ -4254,10 +4254,10 @@
         <v>47</v>
       </c>
       <c r="E63" s="2">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F63" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>61</v>

--- a/config/永泰_2_BCU.xlsx
+++ b/config/永泰_2_BCU.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="221">
   <si>
     <t>序号</t>
   </si>
@@ -175,6 +175,120 @@
     <t>0x40c017c</t>
   </si>
   <si>
+    <t>系统状态</t>
+  </si>
+  <si>
+    <t>0x40c0080</t>
+  </si>
+  <si>
+    <t>预上电阶段/运行状态</t>
+  </si>
+  <si>
+    <t>电压片段1</t>
+  </si>
+  <si>
+    <t>0x40c0086</t>
+  </si>
+  <si>
+    <t>总压/压差/预充/最高单体电压</t>
+  </si>
+  <si>
+    <t>电压片段2</t>
+  </si>
+  <si>
+    <t>0x40c008a</t>
+  </si>
+  <si>
+    <t>最高单体编号/从控/最低单体电压</t>
+  </si>
+  <si>
+    <t>电压片段3</t>
+  </si>
+  <si>
+    <t>0x40c008e</t>
+  </si>
+  <si>
+    <t>最低单体编号/从控/压差</t>
+  </si>
+  <si>
+    <t>电压片段4</t>
+  </si>
+  <si>
+    <t>0x40c0092</t>
+  </si>
+  <si>
+    <t>平均电压/最高温度/编号/从控</t>
+  </si>
+  <si>
+    <t>温度片段1</t>
+  </si>
+  <si>
+    <t>0x40c0096</t>
+  </si>
+  <si>
+    <t>最高温度从控内编号/最低温度/编号/从控</t>
+  </si>
+  <si>
+    <t>温度片段2</t>
+  </si>
+  <si>
+    <t>0x40c009a</t>
+  </si>
+  <si>
+    <t>最低温度从控内编号/平均/极柱温度/编号</t>
+  </si>
+  <si>
+    <t>电流SOC</t>
+  </si>
+  <si>
+    <t>0x40c009e</t>
+  </si>
+  <si>
+    <t>最大充放电电流/SOC/SOH</t>
+  </si>
+  <si>
+    <t>充放状态</t>
+  </si>
+  <si>
+    <t>0x40c00a8</t>
+  </si>
+  <si>
+    <t>充放电状态</t>
+  </si>
+  <si>
+    <t>充满放空</t>
+  </si>
+  <si>
+    <t>0x40c00af</t>
+  </si>
+  <si>
+    <t>充满放空标志</t>
+  </si>
+  <si>
+    <t>电量片段1</t>
+  </si>
+  <si>
+    <t>0x40c00b3</t>
+  </si>
+  <si>
+    <t>可充/可放/最近充/最近放电量</t>
+  </si>
+  <si>
+    <t>电量片段2</t>
+  </si>
+  <si>
+    <t>0x40c00b7</t>
+  </si>
+  <si>
+    <t>累计充电量高/低16位;累计放电量高/低16位</t>
+  </si>
+  <si>
+    <t>启停机</t>
+  </si>
+  <si>
+    <t>0x40b0011</t>
+  </si>
+  <si>
     <t>点号</t>
   </si>
   <si>
@@ -211,18 +325,162 @@
     <t>枚举定义</t>
   </si>
   <si>
+    <t>预上电阶段</t>
+  </si>
+  <si>
+    <t>MOTOROLA</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>0:断网;1:启动并网;2:并网中;3:并网成功;4:并网失败</t>
+  </si>
+  <si>
+    <t>运行状态</t>
+  </si>
+  <si>
+    <t>0:正常;1:禁充;2:禁放;3:待机;4:停机</t>
+  </si>
+  <si>
+    <t>单体累加和总压</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>采集总压与累加总压差</t>
+  </si>
+  <si>
+    <t>预充总压</t>
+  </si>
+  <si>
+    <t>单体最高电压</t>
+  </si>
+  <si>
+    <t>单体最高电压编号</t>
+  </si>
+  <si>
+    <t>最高单体所在从控号</t>
+  </si>
+  <si>
+    <t>最高单体在从控中的单体编号</t>
+  </si>
+  <si>
+    <t>单体最低电压</t>
+  </si>
+  <si>
+    <t>单体最低电压编号</t>
+  </si>
+  <si>
+    <t>最低单体所在从控编号</t>
+  </si>
+  <si>
+    <t>最低单体在从控中的单体编号</t>
+  </si>
+  <si>
+    <t>最高最低单体压差</t>
+  </si>
+  <si>
+    <t>单体平均电压</t>
+  </si>
+  <si>
+    <t>电池最高温度</t>
+  </si>
+  <si>
+    <t>I16</t>
+  </si>
+  <si>
+    <t>℃</t>
+  </si>
+  <si>
+    <t>电池最高温度编号</t>
+  </si>
+  <si>
+    <t>最高温度所在从控编号</t>
+  </si>
+  <si>
+    <t>最高温度在从控中的温度编号</t>
+  </si>
+  <si>
+    <t>电池最低温度</t>
+  </si>
+  <si>
+    <t>电池最低温度编号</t>
+  </si>
+  <si>
+    <t>最低温度所在从控编号</t>
+  </si>
+  <si>
+    <t>最低温度在从控中的温度编号</t>
+  </si>
+  <si>
+    <t>平均温度</t>
+  </si>
+  <si>
+    <t>最大极柱温度</t>
+  </si>
+  <si>
+    <t>最大极柱温度编号</t>
+  </si>
+  <si>
+    <t>最大可接受充电电流</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>最大可接受放电电流</t>
+  </si>
+  <si>
+    <t>显示SOC</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>SOH</t>
+  </si>
+  <si>
+    <t>0:静置;1:放电;2:充电</t>
+  </si>
+  <si>
+    <t>bit0:充满;bit1:放空</t>
+  </si>
+  <si>
+    <t>可充电量</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>可放电量</t>
+  </si>
+  <si>
+    <t>最近一次充电量</t>
+  </si>
+  <si>
+    <t>最近一次放电量</t>
+  </si>
+  <si>
+    <t>累计充电量高16位</t>
+  </si>
+  <si>
+    <t>累计充电量低16位</t>
+  </si>
+  <si>
+    <t>累计放电量高16位</t>
+  </si>
+  <si>
+    <t>累计放电量低16位</t>
+  </si>
+  <si>
     <t>总电压过高严重报警</t>
   </si>
   <si>
-    <t>MOTOROLA</t>
-  </si>
-  <si>
-    <t>U16</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
     <t>总电压过高中度报警</t>
   </si>
   <si>
@@ -262,9 +520,6 @@
     <t>SOC 过低严重报警</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>SOC 过低中度报警</t>
   </si>
   <si>
@@ -292,9 +547,6 @@
     <t>高压箱温度过高严重告警</t>
   </si>
   <si>
-    <t>℃</t>
-  </si>
-  <si>
     <t>高压箱温度过高中度告警</t>
   </si>
   <si>
@@ -401,9 +653,6 @@
   </si>
   <si>
     <t>放电电流过大严重报警</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
   <si>
     <t>放电电流过大中度报警</t>
@@ -928,153 +1177,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1082,12 +1331,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1617,13 +1860,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="9.11111111111111" style="2"/>
+    <col min="1" max="1" width="9.11111111111111" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.9603174603175" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.9285714285714" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.11111111111111" style="2"/>
+    <col min="4" max="11" width="9.11111111111111" style="2" customWidth="1"/>
+    <col min="12" max="12" width="37.031746031746" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9.11111111111111" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
@@ -2189,7 +2434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:12">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2221,6 +2466,497 @@
         <v>17</v>
       </c>
       <c r="K17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="2">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="2">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="2">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="2">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="2">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="2">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="2">
+        <v>8</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="2">
+        <v>8</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="2">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="2">
+        <v>8</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="2">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2233,59 +2969,60 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="9.11111111111111" style="2"/>
+    <col min="1" max="1" width="9.11111111111111" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.547619047619" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.9285714285714" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.3174603174603" style="2" customWidth="1"/>
-    <col min="5" max="6" width="9.11111111111111" style="2"/>
+    <col min="5" max="6" width="9.11111111111111" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.7936507936508" style="2" customWidth="1"/>
-    <col min="8" max="12" width="9.11111111111111" style="2"/>
-    <col min="13" max="13" width="21.6031746031746" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9.11111111111111" style="2"/>
+    <col min="8" max="11" width="9.11111111111111" style="2" customWidth="1"/>
+    <col min="12" max="12" width="6.57936507936508" style="2" customWidth="1"/>
+    <col min="13" max="13" width="43.9920634920635" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.11111111111111" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>59</v>
+        <v>96</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
@@ -2293,13 +3030,13 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>98</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E2" s="2">
         <v>7</v>
@@ -2308,30 +3045,33 @@
         <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>63</v>
+        <v>101</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="2">
-        <v>1001</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>103</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="E3" s="2">
         <v>23</v>
@@ -2340,42 +3080,45 @@
         <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>63</v>
+        <v>101</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="2">
-        <v>1002</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>105</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="E4" s="2">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
         <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2">
         <v>0.1</v>
@@ -2384,30 +3127,30 @@
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="2">
-        <v>1003</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
+        <v>107</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="E5" s="2">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2">
         <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2">
         <v>0.1</v>
@@ -2416,30 +3159,30 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="2">
-        <v>1004</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F6" s="2">
         <v>16</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2">
         <v>0.1</v>
@@ -2448,190 +3191,190 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="2">
-        <v>1005</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="E7" s="2">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2">
         <v>16</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I7" s="2">
-        <v>0.1</v>
+        <v>0.001</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="2">
-        <v>1006</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2">
         <v>16</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="2">
-        <v>1007</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E9" s="2">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="F9" s="2">
         <v>16</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="2">
-        <v>1008</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F10" s="2">
         <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2">
         <v>0</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="2">
-        <v>1009</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F11" s="2">
         <v>16</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I11" s="2">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="2">
-        <v>1010</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2">
         <v>16</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
@@ -2640,30 +3383,30 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="2">
-        <v>1011</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="F13" s="2">
         <v>16</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
@@ -2672,30 +3415,30 @@
         <v>0</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="2">
-        <v>1012</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F14" s="2">
         <v>16</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
@@ -2704,350 +3447,350 @@
         <v>0</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="2">
-        <v>1013</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F15" s="2">
         <v>16</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="2">
-        <v>1014</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="2">
+        <v>7</v>
+      </c>
+      <c r="F16" s="2">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.001</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2">
         <v>23</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F17" s="2">
+        <v>16</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="2">
         <v>39</v>
       </c>
-      <c r="F16" s="2">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="F18" s="2">
+        <v>16</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="2">
-        <v>1015</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="E19" s="2">
+        <v>55</v>
+      </c>
+      <c r="F19" s="2">
+        <v>16</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="2">
+        <v>7</v>
+      </c>
+      <c r="F20" s="2">
+        <v>16</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="2">
         <v>23</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F21" s="2">
+        <v>16</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="2">
+        <v>39</v>
+      </c>
+      <c r="F22" s="2">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="2">
         <v>55</v>
       </c>
-      <c r="F17" s="2">
-        <v>16</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="2">
-        <v>1016</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="2">
+      <c r="F23" s="2">
+        <v>16</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="2">
         <v>7</v>
       </c>
-      <c r="F18" s="2">
-        <v>16</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="2">
-        <v>1017</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="F24" s="2">
+        <v>16</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="2">
         <v>23</v>
       </c>
-      <c r="F19" s="2">
-        <v>16</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="2">
-        <v>1018</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="2">
-        <v>39</v>
-      </c>
-      <c r="F20" s="2">
-        <v>16</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2">
-        <v>0</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="2">
-        <v>1019</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="2">
-        <v>55</v>
-      </c>
-      <c r="F21" s="2">
-        <v>16</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="2">
-        <v>1020</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="2">
-        <v>7</v>
-      </c>
-      <c r="F22" s="2">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="2">
-        <v>1021</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="2">
-        <v>23</v>
-      </c>
-      <c r="F23" s="2">
-        <v>16</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="2">
-        <v>1022</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="2">
-        <v>39</v>
-      </c>
-      <c r="F24" s="2">
-        <v>16</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="2">
-        <v>1023</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="2">
-        <v>55</v>
-      </c>
       <c r="F25" s="2">
         <v>16</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="I25" s="2">
         <v>0.1</v>
@@ -3056,254 +3799,257 @@
         <v>0</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="2">
-        <v>1024</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="2">
+        <v>39</v>
+      </c>
+      <c r="F26" s="2">
+        <v>16</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="2">
+        <v>55</v>
+      </c>
+      <c r="F27" s="2">
+        <v>16</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="2">
+        <v>7</v>
+      </c>
+      <c r="F28" s="2">
+        <v>16</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="2">
+        <v>23</v>
+      </c>
+      <c r="F29" s="2">
+        <v>16</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="E26" s="2">
+      <c r="B30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="2">
+        <v>39</v>
+      </c>
+      <c r="F30" s="2">
+        <v>16</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="2">
+        <v>55</v>
+      </c>
+      <c r="F31" s="2">
+        <v>16</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2">
         <v>7</v>
       </c>
-      <c r="F26" s="2">
-        <v>16</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="2">
-        <v>1025</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="2">
-        <v>23</v>
-      </c>
-      <c r="F27" s="2">
-        <v>16</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I27" s="2">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="2">
-        <v>1026</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="2">
-        <v>39</v>
-      </c>
-      <c r="F28" s="2">
-        <v>16</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2">
-        <v>0</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="2">
-        <v>1027</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="2">
-        <v>55</v>
-      </c>
-      <c r="F29" s="2">
-        <v>16</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2">
-        <v>0</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="2">
-        <v>1028</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="F32" s="2">
+        <v>16</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="2">
         <v>7</v>
       </c>
-      <c r="F30" s="2">
-        <v>16</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I30" s="2">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="2">
-        <v>1029</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" s="2">
-        <v>23</v>
-      </c>
-      <c r="F31" s="2">
-        <v>16</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I31" s="2">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="2">
-        <v>1030</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="2">
-        <v>39</v>
-      </c>
-      <c r="F32" s="2">
-        <v>16</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="2">
-        <v>1031</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="2">
-        <v>55</v>
-      </c>
       <c r="F33" s="2">
         <v>16</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I33" s="2">
         <v>1</v>
@@ -3312,18 +4058,21 @@
         <v>0</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>101</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="2">
-        <v>1032</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="E34" s="2">
         <v>7</v>
@@ -3332,10 +4081,10 @@
         <v>16</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I34" s="2">
         <v>1</v>
@@ -3344,18 +4093,18 @@
         <v>0</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="2">
-        <v>1033</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2">
         <v>23</v>
@@ -3364,10 +4113,10 @@
         <v>16</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I35" s="2">
         <v>1</v>
@@ -3376,18 +4125,18 @@
         <v>0</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="2">
-        <v>1034</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2">
         <v>39</v>
@@ -3396,10 +4145,10 @@
         <v>16</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I36" s="2">
         <v>1</v>
@@ -3408,18 +4157,18 @@
         <v>0</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="2">
-        <v>1035</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="E37" s="2">
         <v>55</v>
@@ -3428,30 +4177,30 @@
         <v>16</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I37" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="2">
-        <v>1036</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2">
         <v>7</v>
@@ -3460,30 +4209,30 @@
         <v>16</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I38" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="2">
-        <v>1037</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2">
         <v>23</v>
@@ -3492,30 +4241,30 @@
         <v>16</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I39" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="2">
-        <v>1038</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2">
         <v>39</v>
@@ -3524,30 +4273,30 @@
         <v>16</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I40" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="2">
-        <v>1039</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2">
         <v>55</v>
@@ -3556,30 +4305,30 @@
         <v>16</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I41" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J41" s="2">
         <v>0</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="2">
-        <v>1040</v>
+        <v>1000</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>37</v>
+        <v>149</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E42" s="2">
         <v>7</v>
@@ -3588,10 +4337,10 @@
         <v>16</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I42" s="2">
         <v>0.1</v>
@@ -3600,18 +4349,18 @@
         <v>0</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="2">
-        <v>1041</v>
+        <v>1001</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>37</v>
+        <v>150</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E43" s="2">
         <v>23</v>
@@ -3620,10 +4369,10 @@
         <v>16</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I43" s="2">
         <v>0.1</v>
@@ -3632,18 +4381,18 @@
         <v>0</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="2">
-        <v>1042</v>
+        <v>1002</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>37</v>
+        <v>151</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E44" s="2">
         <v>39</v>
@@ -3652,10 +4401,10 @@
         <v>16</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I44" s="2">
         <v>0.1</v>
@@ -3664,18 +4413,18 @@
         <v>0</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="2">
-        <v>1043</v>
+        <v>1003</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>37</v>
+        <v>152</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E45" s="2">
         <v>55</v>
@@ -3684,10 +4433,10 @@
         <v>16</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I45" s="2">
         <v>0.1</v>
@@ -3696,18 +4445,18 @@
         <v>0</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="2">
-        <v>1044</v>
+        <v>1004</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E46" s="2">
         <v>7</v>
@@ -3716,10 +4465,10 @@
         <v>16</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I46" s="2">
         <v>0.1</v>
@@ -3728,18 +4477,18 @@
         <v>0</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="2">
-        <v>1045</v>
+        <v>1005</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>39</v>
+        <v>154</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E47" s="2">
         <v>23</v>
@@ -3748,10 +4497,10 @@
         <v>16</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I47" s="2">
         <v>0.1</v>
@@ -3760,18 +4509,18 @@
         <v>0</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="2">
-        <v>1046</v>
+        <v>1006</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>39</v>
+        <v>155</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E48" s="2">
         <v>39</v>
@@ -3780,10 +4529,10 @@
         <v>16</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I48" s="2">
         <v>0.1</v>
@@ -3792,18 +4541,18 @@
         <v>0</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2">
-        <v>1047</v>
+        <v>1007</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>39</v>
+        <v>156</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E49" s="2">
         <v>55</v>
@@ -3812,10 +4561,10 @@
         <v>16</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I49" s="2">
         <v>0.1</v>
@@ -3824,18 +4573,18 @@
         <v>0</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2">
-        <v>1048</v>
+        <v>1008</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2">
         <v>7</v>
@@ -3843,31 +4592,31 @@
       <c r="F50" s="2">
         <v>16</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I50" s="5">
+      <c r="G50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I50" s="2">
         <v>0.1</v>
       </c>
-      <c r="J50" s="5">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5" t="s">
-        <v>87</v>
+      <c r="J50" s="2">
+        <v>0</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2">
-        <v>1049</v>
+        <v>1009</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2">
         <v>23</v>
@@ -3875,31 +4624,31 @@
       <c r="F51" s="2">
         <v>16</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I51" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J51" s="5">
-        <v>0</v>
-      </c>
-      <c r="K51" s="5" t="s">
-        <v>87</v>
+      <c r="G51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2">
+        <v>0</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2">
-        <v>1050</v>
+        <v>1010</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2">
         <v>39</v>
@@ -3907,31 +4656,31 @@
       <c r="F52" s="2">
         <v>16</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I52" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J52" s="5">
-        <v>0</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>87</v>
+      <c r="G52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2">
+        <v>0</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="2">
-        <v>1051</v>
+        <v>1011</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2">
         <v>55</v>
@@ -3939,31 +4688,31 @@
       <c r="F53" s="2">
         <v>16</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I53" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J53" s="5">
-        <v>0</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>87</v>
+      <c r="G53" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+      <c r="J53" s="2">
+        <v>0</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2">
-        <v>1052</v>
+        <v>1012</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E54" s="2">
         <v>7</v>
@@ -3971,31 +4720,31 @@
       <c r="F54" s="2">
         <v>16</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I54" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J54" s="5">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5" t="s">
-        <v>87</v>
+      <c r="G54" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2">
-        <v>1053</v>
+        <v>1013</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>43</v>
+        <v>163</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E55" s="2">
         <v>23</v>
@@ -4003,31 +4752,31 @@
       <c r="F55" s="2">
         <v>16</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I55" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J55" s="5">
-        <v>0</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>87</v>
+      <c r="G55" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I55" s="2">
+        <v>1</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2">
-        <v>1054</v>
+        <v>1014</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E56" s="2">
         <v>39</v>
@@ -4035,31 +4784,31 @@
       <c r="F56" s="2">
         <v>16</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I56" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J56" s="5">
-        <v>0</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>87</v>
+      <c r="G56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2">
-        <v>1055</v>
+        <v>1015</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E57" s="2">
         <v>55</v>
@@ -4067,31 +4816,31 @@
       <c r="F57" s="2">
         <v>16</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I57" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J57" s="5">
-        <v>0</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>87</v>
+      <c r="G57" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I57" s="2">
+        <v>1</v>
+      </c>
+      <c r="J57" s="2">
+        <v>0</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2">
-        <v>1056</v>
+        <v>1016</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E58" s="2">
         <v>7</v>
@@ -4099,31 +4848,31 @@
       <c r="F58" s="2">
         <v>16</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I58" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J58" s="5">
-        <v>0</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>124</v>
+      <c r="G58" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I58" s="2">
+        <v>1</v>
+      </c>
+      <c r="J58" s="2">
+        <v>0</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2">
-        <v>1057</v>
+        <v>1017</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>45</v>
+        <v>167</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E59" s="2">
         <v>23</v>
@@ -4131,31 +4880,31 @@
       <c r="F59" s="2">
         <v>16</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I59" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J59" s="5">
-        <v>0</v>
-      </c>
-      <c r="K59" s="5" t="s">
-        <v>124</v>
+      <c r="G59" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I59" s="2">
+        <v>1</v>
+      </c>
+      <c r="J59" s="2">
+        <v>0</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2">
-        <v>1058</v>
+        <v>1018</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>45</v>
+        <v>168</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E60" s="2">
         <v>39</v>
@@ -4163,31 +4912,31 @@
       <c r="F60" s="2">
         <v>16</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I60" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J60" s="5">
-        <v>0</v>
-      </c>
-      <c r="K60" s="5" t="s">
-        <v>124</v>
+      <c r="G60" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I60" s="2">
+        <v>1</v>
+      </c>
+      <c r="J60" s="2">
+        <v>0</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2">
-        <v>1059</v>
+        <v>1019</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>45</v>
+        <v>169</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E61" s="2">
         <v>55</v>
@@ -4195,31 +4944,31 @@
       <c r="F61" s="2">
         <v>16</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I61" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J61" s="5">
-        <v>0</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>124</v>
+      <c r="G61" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I61" s="2">
+        <v>1</v>
+      </c>
+      <c r="J61" s="2">
+        <v>0</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2">
-        <v>1060</v>
+        <v>1020</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E62" s="2">
         <v>7</v>
@@ -4227,31 +4976,31 @@
       <c r="F62" s="2">
         <v>16</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I62" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="J62" s="5">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5" t="s">
-        <v>124</v>
+      <c r="G62" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I62" s="2">
+        <v>1</v>
+      </c>
+      <c r="J62" s="2">
+        <v>0</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2">
-        <v>1061</v>
+        <v>1021</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>47</v>
+        <v>171</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E63" s="2">
         <v>23</v>
@@ -4259,20 +5008,1329 @@
       <c r="F63" s="2">
         <v>16</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I63" s="5">
+      <c r="G63" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I63" s="2">
         <v>0.1</v>
       </c>
-      <c r="J63" s="5">
-        <v>0</v>
-      </c>
-      <c r="K63" s="5" t="s">
-        <v>124</v>
+      <c r="J63" s="2">
+        <v>0</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" s="2">
+        <v>1022</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" s="2">
+        <v>39</v>
+      </c>
+      <c r="F64" s="2">
+        <v>16</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="2">
+        <v>1023</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="2">
+        <v>55</v>
+      </c>
+      <c r="F65" s="2">
+        <v>16</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J65" s="2">
+        <v>0</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="2">
+        <v>1024</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="2">
+        <v>7</v>
+      </c>
+      <c r="F66" s="2">
+        <v>16</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I66" s="2">
+        <v>1</v>
+      </c>
+      <c r="J66" s="2">
+        <v>0</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" s="2">
+        <v>1025</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="2">
+        <v>23</v>
+      </c>
+      <c r="F67" s="2">
+        <v>16</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I67" s="2">
+        <v>1</v>
+      </c>
+      <c r="J67" s="2">
+        <v>0</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" s="2">
+        <v>1026</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="2">
+        <v>39</v>
+      </c>
+      <c r="F68" s="2">
+        <v>16</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I68" s="2">
+        <v>1</v>
+      </c>
+      <c r="J68" s="2">
+        <v>0</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="2">
+        <v>1027</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="2">
+        <v>55</v>
+      </c>
+      <c r="F69" s="2">
+        <v>16</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I69" s="2">
+        <v>1</v>
+      </c>
+      <c r="J69" s="2">
+        <v>0</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="2">
+        <v>1028</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" s="2">
+        <v>7</v>
+      </c>
+      <c r="F70" s="2">
+        <v>16</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I70" s="2">
+        <v>1</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="2">
+        <v>1029</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" s="2">
+        <v>23</v>
+      </c>
+      <c r="F71" s="2">
+        <v>16</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I71" s="2">
+        <v>1</v>
+      </c>
+      <c r="J71" s="2">
+        <v>0</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="2">
+        <v>1030</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E72" s="2">
+        <v>39</v>
+      </c>
+      <c r="F72" s="2">
+        <v>16</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I72" s="2">
+        <v>1</v>
+      </c>
+      <c r="J72" s="2">
+        <v>0</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="2">
+        <v>1031</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="2">
+        <v>55</v>
+      </c>
+      <c r="F73" s="2">
+        <v>16</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I73" s="2">
+        <v>1</v>
+      </c>
+      <c r="J73" s="2">
+        <v>0</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="2">
+        <v>1032</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74" s="2">
+        <v>7</v>
+      </c>
+      <c r="F74" s="2">
+        <v>16</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I74" s="2">
+        <v>1</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="2">
+        <v>1033</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E75" s="2">
+        <v>23</v>
+      </c>
+      <c r="F75" s="2">
+        <v>16</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I75" s="2">
+        <v>1</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="2">
+        <v>1034</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E76" s="2">
+        <v>39</v>
+      </c>
+      <c r="F76" s="2">
+        <v>16</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I76" s="2">
+        <v>1</v>
+      </c>
+      <c r="J76" s="2">
+        <v>0</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="2">
+        <v>1035</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E77" s="2">
+        <v>55</v>
+      </c>
+      <c r="F77" s="2">
+        <v>16</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J77" s="2">
+        <v>0</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="2">
+        <v>1036</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="2">
+        <v>7</v>
+      </c>
+      <c r="F78" s="2">
+        <v>16</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="2">
+        <v>1037</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="2">
+        <v>23</v>
+      </c>
+      <c r="F79" s="2">
+        <v>16</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="2">
+        <v>1038</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="2">
+        <v>39</v>
+      </c>
+      <c r="F80" s="2">
+        <v>16</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="2">
+        <v>1039</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="2">
+        <v>55</v>
+      </c>
+      <c r="F81" s="2">
+        <v>16</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="2">
+        <v>1040</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E82" s="2">
+        <v>7</v>
+      </c>
+      <c r="F82" s="2">
+        <v>16</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="2">
+        <v>1041</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E83" s="2">
+        <v>23</v>
+      </c>
+      <c r="F83" s="2">
+        <v>16</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J83" s="2">
+        <v>0</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="2">
+        <v>1042</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E84" s="2">
+        <v>39</v>
+      </c>
+      <c r="F84" s="2">
+        <v>16</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J84" s="2">
+        <v>0</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="2">
+        <v>1043</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E85" s="2">
+        <v>55</v>
+      </c>
+      <c r="F85" s="2">
+        <v>16</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="2">
+        <v>1044</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E86" s="2">
+        <v>7</v>
+      </c>
+      <c r="F86" s="2">
+        <v>16</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J86" s="2">
+        <v>0</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="2">
+        <v>1045</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E87" s="2">
+        <v>23</v>
+      </c>
+      <c r="F87" s="2">
+        <v>16</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J87" s="2">
+        <v>0</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="2">
+        <v>1046</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E88" s="2">
+        <v>39</v>
+      </c>
+      <c r="F88" s="2">
+        <v>16</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J88" s="2">
+        <v>0</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="2">
+        <v>1047</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E89" s="2">
+        <v>55</v>
+      </c>
+      <c r="F89" s="2">
+        <v>16</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J89" s="2">
+        <v>0</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="2">
+        <v>1048</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" s="2">
+        <v>7</v>
+      </c>
+      <c r="F90" s="2">
+        <v>16</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I90" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J90" s="3">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="2">
+        <v>1049</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" s="2">
+        <v>23</v>
+      </c>
+      <c r="F91" s="2">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="2">
+        <v>1050</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" s="2">
+        <v>39</v>
+      </c>
+      <c r="F92" s="2">
+        <v>16</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I92" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="2">
+        <v>1051</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93" s="2">
+        <v>55</v>
+      </c>
+      <c r="F93" s="2">
+        <v>16</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I93" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J93" s="3">
+        <v>0</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="2">
+        <v>1052</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E94" s="2">
+        <v>7</v>
+      </c>
+      <c r="F94" s="2">
+        <v>16</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="2">
+        <v>1053</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E95" s="2">
+        <v>23</v>
+      </c>
+      <c r="F95" s="2">
+        <v>16</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I95" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J95" s="3">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="2">
+        <v>1054</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="2">
+        <v>39</v>
+      </c>
+      <c r="F96" s="2">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" s="2">
+        <v>1055</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="2">
+        <v>55</v>
+      </c>
+      <c r="F97" s="2">
+        <v>16</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I97" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" s="2">
+        <v>1056</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E98" s="2">
+        <v>7</v>
+      </c>
+      <c r="F98" s="2">
+        <v>16</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I98" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J98" s="3">
+        <v>0</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" s="2">
+        <v>1057</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E99" s="2">
+        <v>23</v>
+      </c>
+      <c r="F99" s="2">
+        <v>16</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I99" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J99" s="3">
+        <v>0</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="2">
+        <v>1058</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" s="2">
+        <v>39</v>
+      </c>
+      <c r="F100" s="2">
+        <v>16</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" s="2">
+        <v>1059</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E101" s="2">
+        <v>55</v>
+      </c>
+      <c r="F101" s="2">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" s="2">
+        <v>1060</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E102" s="2">
+        <v>7</v>
+      </c>
+      <c r="F102" s="2">
+        <v>16</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="2">
+        <v>1061</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E103" s="2">
+        <v>23</v>
+      </c>
+      <c r="F103" s="2">
+        <v>16</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I103" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J103" s="3">
+        <v>0</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" s="2">
+        <v>3000</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E104" s="2">
+        <v>7</v>
+      </c>
+      <c r="F104" s="2">
+        <v>16</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I104" s="2">
+        <v>1</v>
+      </c>
+      <c r="J104" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4287,66 +6345,66 @@
   <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="9.11111111111111" style="2"/>
+    <col min="1" max="2" width="9.11111111111111" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.2460317460317" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.8809523809524" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.8015873015873" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.8809523809524" style="2" customWidth="1"/>
-    <col min="7" max="8" width="9.11111111111111" style="2"/>
+    <col min="7" max="8" width="9.11111111111111" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.531746031746" style="2" customWidth="1"/>
     <col min="10" max="10" width="12.952380952381" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.7380952380952" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9.11111111111111" style="2"/>
+    <col min="12" max="16384" width="9.11111111111111" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>136</v>
+        <v>219</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>11</v>

--- a/config/永泰_2_BCU.xlsx
+++ b/config/永泰_2_BCU.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="224">
   <si>
     <t>序号</t>
   </si>
@@ -67,21 +67,42 @@
     <t>备注</t>
   </si>
   <si>
+    <t>主控控制</t>
+  </si>
+  <si>
+    <t>0x4090000</t>
+  </si>
+  <si>
+    <t>extended</t>
+  </si>
+  <si>
+    <t>EMS</t>
+  </si>
+  <si>
+    <t>BMS</t>
+  </si>
+  <si>
+    <t>trigger</t>
+  </si>
+  <si>
+    <t>绝缘采样</t>
+  </si>
+  <si>
+    <t>0x4090010</t>
+  </si>
+  <si>
+    <t>启停机</t>
+  </si>
+  <si>
+    <t>0x4090011</t>
+  </si>
+  <si>
     <t>告警片段1</t>
   </si>
   <si>
     <t>0x40c0140</t>
   </si>
   <si>
-    <t>extended</t>
-  </si>
-  <si>
-    <t>BMS</t>
-  </si>
-  <si>
-    <t>EMS</t>
-  </si>
-  <si>
     <t>cycle</t>
   </si>
   <si>
@@ -283,12 +304,6 @@
     <t>累计充电量高/低16位;累计放电量高/低16位</t>
   </si>
   <si>
-    <t>启停机</t>
-  </si>
-  <si>
-    <t>0x40b0011</t>
-  </si>
-  <si>
     <t>点号</t>
   </si>
   <si>
@@ -325,18 +340,15 @@
     <t>枚举定义</t>
   </si>
   <si>
+    <t>MOTOROLA</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
     <t>预上电阶段</t>
   </si>
   <si>
-    <t>MOTOROLA</t>
-  </si>
-  <si>
-    <t>U16</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>0:断网;1:启动并网;2:并网中;3:并网成功;4:并网失败</t>
   </si>
   <si>
@@ -466,16 +478,13 @@
     <t>最近一次放电量</t>
   </si>
   <si>
-    <t>累计充电量高16位</t>
-  </si>
-  <si>
-    <t>累计充电量低16位</t>
-  </si>
-  <si>
-    <t>累计放电量高16位</t>
-  </si>
-  <si>
-    <t>累计放电量低16位</t>
+    <t>累计充电量</t>
+  </si>
+  <si>
+    <t>U32</t>
+  </si>
+  <si>
+    <t>累计放电量</t>
   </si>
   <si>
     <t>总电压过高严重报警</t>
@@ -1322,7 +1331,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1330,6 +1339,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1860,7 +1872,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2" customWidth="1"/>
@@ -1909,113 +1921,113 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" s="3" customFormat="1" spans="1:12">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="E2" s="4">
+        <v>2</v>
+      </c>
+      <c r="F2" s="4">
         <v>1000</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="4">
         <v>1000</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="2">
+      <c r="K2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:12">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2">
-        <v>8</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="E3" s="4">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4">
         <v>1000</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="4">
         <v>1000</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="I3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="2">
+      <c r="K3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:12">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
         <v>1000</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="4">
         <v>1000</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -2037,27 +2049,27 @@
         <v>1000</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -2072,27 +2084,27 @@
         <v>1000</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -2107,27 +2119,27 @@
         <v>1000</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J7" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -2142,27 +2154,27 @@
         <v>1000</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -2177,27 +2189,27 @@
         <v>1000</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -2212,27 +2224,27 @@
         <v>1000</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
@@ -2247,27 +2259,27 @@
         <v>1000</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -2282,27 +2294,27 @@
         <v>1000</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -2317,27 +2329,27 @@
         <v>1000</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -2352,27 +2364,27 @@
         <v>1000</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K14" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -2387,27 +2399,27 @@
         <v>1000</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>
@@ -2422,27 +2434,27 @@
         <v>1000</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
@@ -2457,27 +2469,27 @@
         <v>1000</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="K17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>14</v>
@@ -2492,23 +2504,20 @@
         <v>1000</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K18" s="2">
         <v>1</v>
       </c>
-      <c r="L18" s="2" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -2530,30 +2539,27 @@
         <v>1000</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K19" s="2">
         <v>1</v>
       </c>
-      <c r="L19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
@@ -2568,30 +2574,27 @@
         <v>1000</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K20" s="2">
         <v>1</v>
       </c>
-      <c r="L20" s="2" t="s">
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -2606,30 +2609,30 @@
         <v>1000</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K21" s="2">
         <v>1</v>
       </c>
       <c r="L21" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>14</v>
@@ -2644,30 +2647,30 @@
         <v>1000</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J22" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K22" s="2">
         <v>1</v>
       </c>
       <c r="L22" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -2682,30 +2685,30 @@
         <v>1000</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K23" s="2">
         <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -2720,30 +2723,30 @@
         <v>1000</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K24" s="2">
         <v>1</v>
       </c>
       <c r="L24" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
@@ -2758,30 +2761,30 @@
         <v>1000</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K25" s="2">
         <v>1</v>
       </c>
       <c r="L25" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>14</v>
@@ -2796,30 +2799,30 @@
         <v>1000</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K26" s="2">
         <v>1</v>
       </c>
       <c r="L26" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>14</v>
@@ -2834,30 +2837,30 @@
         <v>1000</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
@@ -2872,30 +2875,30 @@
         <v>1000</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K28" s="2">
         <v>1</v>
       </c>
       <c r="L28" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -2910,30 +2913,30 @@
         <v>1000</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J29" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K29" s="2">
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>14</v>
@@ -2954,10 +2957,89 @@
         <v>15</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K30" s="2">
         <v>1</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2">
+        <v>8</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="2">
+        <v>8</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2973,7 +3055,7 @@
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.11111111111111" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.547619047619" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.3412698412698" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.9285714285714" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.3174603174603" style="2" customWidth="1"/>
     <col min="5" max="6" width="9.11111111111111" style="2" customWidth="1"/>
@@ -2986,57 +3068,57 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
+    <row r="2" s="3" customFormat="1" spans="1:14">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E2" s="2">
         <v>7</v>
@@ -3044,46 +3126,40 @@
       <c r="F2" s="2">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>100</v>
+      <c r="G2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
       </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="2">
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:14">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>49</v>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="E3" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
         <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I3" s="2">
         <v>1</v>
@@ -3091,22 +3167,18 @@
       <c r="J3" s="2">
         <v>0</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>104</v>
-      </c>
+      <c r="K3" s="2"/>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>52</v>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="E4" s="2">
         <v>7</v>
@@ -3114,779 +3186,740 @@
       <c r="F4" s="2">
         <v>16</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>100</v>
+      <c r="G4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="I4" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="C6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="2">
         <v>23</v>
       </c>
-      <c r="F5" s="2">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="2">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="2">
-        <v>39</v>
-      </c>
-      <c r="F6" s="2">
-        <v>16</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E7" s="2">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="2">
+        <v>23</v>
+      </c>
+      <c r="F8" s="2">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="2">
+        <v>39</v>
+      </c>
+      <c r="F9" s="2">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="2">
         <v>55</v>
       </c>
-      <c r="F7" s="2">
-        <v>16</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="F10" s="2">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="2">
         <v>0.001</v>
       </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="2">
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="F11" s="2">
+        <v>16</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="2">
+        <v>23</v>
+      </c>
+      <c r="F12" s="2">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="2">
+        <v>39</v>
+      </c>
+      <c r="F13" s="2">
+        <v>16</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="2">
+        <v>55</v>
+      </c>
+      <c r="F14" s="2">
+        <v>16</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.001</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="2">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2">
+        <v>16</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="2">
+        <v>23</v>
+      </c>
+      <c r="F16" s="2">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="2">
+        <v>39</v>
+      </c>
+      <c r="F17" s="2">
+        <v>16</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="2">
         <v>55</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F18" s="2">
+        <v>16</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.001</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="2">
         <v>7</v>
       </c>
-      <c r="F8" s="2">
-        <v>16</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="F19" s="2">
+        <v>16</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.001</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2">
+        <v>23</v>
+      </c>
+      <c r="F20" s="2">
+        <v>16</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="2">
+        <v>39</v>
+      </c>
+      <c r="F21" s="2">
+        <v>16</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="2">
         <v>55</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F22" s="2">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="2">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2">
+        <v>16</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="F9" s="2">
-        <v>16</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="2">
+        <v>23</v>
+      </c>
+      <c r="F24" s="2">
+        <v>16</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="2">
+        <v>39</v>
+      </c>
+      <c r="F25" s="2">
+        <v>16</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="2">
         <v>55</v>
       </c>
-      <c r="E10" s="2">
-        <v>39</v>
-      </c>
-      <c r="F10" s="2">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="2">
-        <v>55</v>
-      </c>
-      <c r="F11" s="2">
-        <v>16</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.001</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="F26" s="2">
+        <v>16</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="2">
         <v>7</v>
       </c>
-      <c r="F12" s="2">
-        <v>16</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="F27" s="2">
+        <v>16</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="2">
         <v>23</v>
       </c>
-      <c r="F13" s="2">
-        <v>16</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="2">
-        <v>39</v>
-      </c>
-      <c r="F14" s="2">
-        <v>16</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="2">
-        <v>55</v>
-      </c>
-      <c r="F15" s="2">
-        <v>16</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0.001</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="2">
-        <v>7</v>
-      </c>
-      <c r="F16" s="2">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0.001</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="2">
-        <v>23</v>
-      </c>
-      <c r="F17" s="2">
-        <v>16</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="2">
-        <v>39</v>
-      </c>
-      <c r="F18" s="2">
-        <v>16</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="2">
-        <v>55</v>
-      </c>
-      <c r="F19" s="2">
-        <v>16</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="F28" s="2">
+        <v>16</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="2">
-        <v>7</v>
-      </c>
-      <c r="F20" s="2">
-        <v>16</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2">
-        <v>0</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="2">
-        <v>23</v>
-      </c>
-      <c r="F21" s="2">
-        <v>16</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="2">
-        <v>39</v>
-      </c>
-      <c r="F22" s="2">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="2">
-        <v>55</v>
-      </c>
-      <c r="F23" s="2">
-        <v>16</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="2">
-        <v>7</v>
-      </c>
-      <c r="F24" s="2">
-        <v>16</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I24" s="2">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="2">
-        <v>23</v>
-      </c>
-      <c r="F25" s="2">
-        <v>16</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J25" s="2">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="2">
-        <v>39</v>
-      </c>
-      <c r="F26" s="2">
-        <v>16</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J26" s="2">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="2">
-        <v>55</v>
-      </c>
-      <c r="F27" s="2">
-        <v>16</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I27" s="2">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="2">
-        <v>7</v>
-      </c>
-      <c r="F28" s="2">
-        <v>16</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="I28" s="2">
         <v>0.1</v>
@@ -3895,30 +3928,30 @@
         <v>0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F29" s="2">
         <v>16</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="I29" s="2">
         <v>0.1</v>
@@ -3927,62 +3960,59 @@
         <v>0</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E30" s="2">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F30" s="2">
         <v>16</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I30" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
-      <c r="K30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="F31" s="2">
         <v>16</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I31" s="2">
         <v>0.1</v>
@@ -3991,388 +4021,382 @@
         <v>0</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2">
+        <v>23</v>
+      </c>
+      <c r="F32" s="2">
+        <v>16</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="2">
+        <v>39</v>
+      </c>
+      <c r="F33" s="2">
+        <v>16</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2">
+        <v>55</v>
+      </c>
+      <c r="F34" s="2">
+        <v>16</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="2">
         <v>7</v>
       </c>
-      <c r="F32" s="2">
-        <v>16</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="2">
+      <c r="F35" s="2">
+        <v>16</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="2">
         <v>7</v>
       </c>
-      <c r="F33" s="2">
-        <v>16</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" s="2">
-        <v>7</v>
-      </c>
-      <c r="F34" s="2">
-        <v>16</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I34" s="2">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35" s="2">
-        <v>23</v>
-      </c>
-      <c r="F35" s="2">
-        <v>16</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="F36" s="2">
+        <v>16</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E36" s="2">
-        <v>39</v>
-      </c>
-      <c r="F36" s="2">
-        <v>16</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E37" s="2">
+        <v>7</v>
+      </c>
+      <c r="F37" s="2">
+        <v>16</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="2">
+        <v>23</v>
+      </c>
+      <c r="F38" s="2">
+        <v>16</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" s="2">
+        <v>39</v>
+      </c>
+      <c r="F39" s="2">
+        <v>16</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I39" s="2">
+        <v>1</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="2">
         <v>55</v>
       </c>
-      <c r="F37" s="2">
-        <v>16</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="F40" s="2">
+        <v>16</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E38" s="2">
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" s="2">
         <v>7</v>
       </c>
-      <c r="F38" s="2">
-        <v>16</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" s="2">
-        <v>23</v>
-      </c>
-      <c r="F39" s="2">
-        <v>16</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I39" s="2">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2">
-        <v>0</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="2">
+      <c r="F41" s="2">
+        <v>32</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I41" s="2">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" s="2">
-        <v>39</v>
-      </c>
-      <c r="F40" s="2">
-        <v>16</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I40" s="2">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E41" s="2">
-        <v>55</v>
-      </c>
-      <c r="F41" s="2">
-        <v>16</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I41" s="2">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2">
-        <v>0</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="2">
-        <v>1000</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="2">
-        <v>7</v>
-      </c>
       <c r="F42" s="2">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I42" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>13</v>
+        <v>152</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E43" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F43" s="2">
         <v>16</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I43" s="2">
         <v>0.1</v>
@@ -4381,30 +4405,30 @@
         <v>0</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>13</v>
+        <v>153</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E44" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F44" s="2">
         <v>16</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I44" s="2">
         <v>0.1</v>
@@ -4413,30 +4437,30 @@
         <v>0</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>13</v>
+        <v>154</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E45" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F45" s="2">
         <v>16</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I45" s="2">
         <v>0.1</v>
@@ -4445,30 +4469,30 @@
         <v>0</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>19</v>
+        <v>155</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="E46" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F46" s="2">
         <v>16</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I46" s="2">
         <v>0.1</v>
@@ -4477,30 +4501,30 @@
         <v>0</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E47" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F47" s="2">
         <v>16</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I47" s="2">
         <v>0.1</v>
@@ -4509,30 +4533,30 @@
         <v>0</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E48" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F48" s="2">
         <v>16</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I48" s="2">
         <v>0.1</v>
@@ -4541,30 +4565,30 @@
         <v>0</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E49" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F49" s="2">
         <v>16</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I49" s="2">
         <v>0.1</v>
@@ -4573,30 +4597,30 @@
         <v>0</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E50" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F50" s="2">
         <v>16</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I50" s="2">
         <v>0.1</v>
@@ -4605,62 +4629,62 @@
         <v>0</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E51" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F51" s="2">
         <v>16</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I51" s="2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J51" s="2">
         <v>0</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E52" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F52" s="2">
         <v>16</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I52" s="2">
         <v>1</v>
@@ -4669,30 +4693,30 @@
         <v>0</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="2">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E53" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F53" s="2">
         <v>16</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I53" s="2">
         <v>1</v>
@@ -4701,62 +4725,62 @@
         <v>0</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" s="2">
+        <v>55</v>
+      </c>
+      <c r="F54" s="2">
+        <v>16</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="2">
-        <v>7</v>
-      </c>
-      <c r="F54" s="2">
-        <v>16</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I54" s="2">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2">
-        <v>0</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E55" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F55" s="2">
         <v>16</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I55" s="2">
         <v>1</v>
@@ -4765,30 +4789,30 @@
         <v>0</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E56" s="2">
         <v>23</v>
       </c>
-      <c r="E56" s="2">
-        <v>39</v>
-      </c>
       <c r="F56" s="2">
         <v>16</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I56" s="2">
         <v>1</v>
@@ -4797,30 +4821,30 @@
         <v>0</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E57" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F57" s="2">
         <v>16</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I57" s="2">
         <v>1</v>
@@ -4829,30 +4853,30 @@
         <v>0</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E58" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F58" s="2">
         <v>16</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I58" s="2">
         <v>1</v>
@@ -4861,30 +4885,30 @@
         <v>0</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E59" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F59" s="2">
         <v>16</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I59" s="2">
         <v>1</v>
@@ -4893,30 +4917,30 @@
         <v>0</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E60" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F60" s="2">
         <v>16</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I60" s="2">
         <v>1</v>
@@ -4925,30 +4949,30 @@
         <v>0</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E61" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F61" s="2">
         <v>16</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I61" s="2">
         <v>1</v>
@@ -4957,30 +4981,30 @@
         <v>0</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E62" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F62" s="2">
         <v>16</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I62" s="2">
         <v>1</v>
@@ -4989,62 +5013,62 @@
         <v>0</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E63" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F63" s="2">
         <v>16</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I63" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J63" s="2">
         <v>0</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E64" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F64" s="2">
         <v>16</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I64" s="2">
         <v>0.1</v>
@@ -5053,30 +5077,30 @@
         <v>0</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E65" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F65" s="2">
         <v>16</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I65" s="2">
         <v>0.1</v>
@@ -5085,62 +5109,62 @@
         <v>0</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E66" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F66" s="2">
         <v>16</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I66" s="2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J66" s="2">
         <v>0</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E67" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F67" s="2">
         <v>16</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I67" s="2">
         <v>1</v>
@@ -5149,30 +5173,30 @@
         <v>0</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E68" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2">
         <v>16</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I68" s="2">
         <v>1</v>
@@ -5181,62 +5205,62 @@
         <v>0</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E69" s="2">
+        <v>39</v>
+      </c>
+      <c r="F69" s="2">
+        <v>16</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I69" s="2">
+        <v>1</v>
+      </c>
+      <c r="J69" s="2">
+        <v>0</v>
+      </c>
+      <c r="K69" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E69" s="2">
-        <v>55</v>
-      </c>
-      <c r="F69" s="2">
-        <v>16</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I69" s="2">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2">
-        <v>0</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E70" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F70" s="2">
         <v>16</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I70" s="2">
         <v>1</v>
@@ -5245,30 +5269,30 @@
         <v>0</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="2">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E71" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F71" s="2">
         <v>16</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I71" s="2">
         <v>1</v>
@@ -5277,30 +5301,30 @@
         <v>0</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E72" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F72" s="2">
         <v>16</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I72" s="2">
         <v>1</v>
@@ -5309,30 +5333,30 @@
         <v>0</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E73" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F73" s="2">
         <v>16</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I73" s="2">
         <v>1</v>
@@ -5341,30 +5365,30 @@
         <v>0</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="2">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E74" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F74" s="2">
         <v>16</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I74" s="2">
         <v>1</v>
@@ -5373,30 +5397,30 @@
         <v>0</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="2">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E75" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F75" s="2">
         <v>16</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I75" s="2">
         <v>1</v>
@@ -5405,30 +5429,30 @@
         <v>0</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="2">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E76" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F76" s="2">
         <v>16</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I76" s="2">
         <v>1</v>
@@ -5437,62 +5461,62 @@
         <v>0</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="2">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E77" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F77" s="2">
         <v>16</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I77" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J77" s="2">
         <v>0</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E78" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F78" s="2">
         <v>16</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I78" s="2">
         <v>0.1</v>
@@ -5501,30 +5525,30 @@
         <v>0</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E79" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F79" s="2">
         <v>16</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I79" s="2">
         <v>0.1</v>
@@ -5533,30 +5557,30 @@
         <v>0</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E80" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F80" s="2">
         <v>16</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I80" s="2">
         <v>0.1</v>
@@ -5565,30 +5589,30 @@
         <v>0</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="2">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E81" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F81" s="2">
         <v>16</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I81" s="2">
         <v>0.1</v>
@@ -5597,30 +5621,30 @@
         <v>0</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="2">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E82" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F82" s="2">
         <v>16</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I82" s="2">
         <v>0.1</v>
@@ -5629,30 +5653,30 @@
         <v>0</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="2">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E83" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F83" s="2">
         <v>16</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I83" s="2">
         <v>0.1</v>
@@ -5661,30 +5685,30 @@
         <v>0</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E84" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F84" s="2">
         <v>16</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I84" s="2">
         <v>0.1</v>
@@ -5693,30 +5717,30 @@
         <v>0</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E85" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F85" s="2">
         <v>16</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I85" s="2">
         <v>0.1</v>
@@ -5725,30 +5749,30 @@
         <v>0</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="2">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E86" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F86" s="2">
         <v>16</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I86" s="2">
         <v>0.1</v>
@@ -5757,30 +5781,30 @@
         <v>0</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>39</v>
+        <v>198</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="E87" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F87" s="2">
         <v>16</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I87" s="2">
         <v>0.1</v>
@@ -5789,30 +5813,30 @@
         <v>0</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>39</v>
+        <v>199</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="E88" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F88" s="2">
         <v>16</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I88" s="2">
         <v>0.1</v>
@@ -5821,30 +5845,30 @@
         <v>0</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C89" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E89" s="2">
         <v>39</v>
       </c>
-      <c r="E89" s="2">
-        <v>55</v>
-      </c>
       <c r="F89" s="2">
         <v>16</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I89" s="2">
         <v>0.1</v>
@@ -5853,484 +5877,487 @@
         <v>0</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="2">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>41</v>
+        <v>201</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="E90" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F90" s="2">
         <v>16</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I90" s="3">
+      <c r="G90" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I90" s="2">
         <v>0.1</v>
       </c>
-      <c r="J90" s="3">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>121</v>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="2">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E91" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F91" s="2">
         <v>16</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="G91" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I91" s="4">
         <v>0.1</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>121</v>
+      <c r="J91" s="4">
+        <v>0</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="2">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E92" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F92" s="2">
         <v>16</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I92" s="3">
+      <c r="G92" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I92" s="4">
         <v>0.1</v>
       </c>
-      <c r="J92" s="3">
-        <v>0</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>121</v>
+      <c r="J92" s="4">
+        <v>0</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="2">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E93" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F93" s="2">
         <v>16</v>
       </c>
-      <c r="G93" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I93" s="3">
+      <c r="G93" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I93" s="4">
         <v>0.1</v>
       </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>121</v>
+      <c r="J93" s="4">
+        <v>0</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E94" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F94" s="2">
         <v>16</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="G94" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I94" s="4">
         <v>0.1</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>121</v>
+      <c r="J94" s="4">
+        <v>0</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>43</v>
+        <v>206</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="E95" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F95" s="2">
         <v>16</v>
       </c>
-      <c r="G95" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I95" s="3">
+      <c r="G95" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I95" s="4">
         <v>0.1</v>
       </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>121</v>
+      <c r="J95" s="4">
+        <v>0</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>43</v>
+        <v>207</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="E96" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F96" s="2">
         <v>16</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="G96" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I96" s="4">
         <v>0.1</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>121</v>
+      <c r="J96" s="4">
+        <v>0</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="2">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E97" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F97" s="2">
         <v>16</v>
       </c>
-      <c r="G97" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I97" s="3">
+      <c r="G97" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I97" s="4">
         <v>0.1</v>
       </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>121</v>
+      <c r="J97" s="4">
+        <v>0</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E98" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F98" s="2">
         <v>16</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I98" s="3">
+      <c r="G98" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I98" s="4">
         <v>0.1</v>
       </c>
-      <c r="J98" s="3">
-        <v>0</v>
-      </c>
-      <c r="K98" s="3" t="s">
-        <v>133</v>
+      <c r="J98" s="4">
+        <v>0</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="2">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>45</v>
+        <v>210</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="E99" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F99" s="2">
         <v>16</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I99" s="3">
+      <c r="G99" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I99" s="4">
         <v>0.1</v>
       </c>
-      <c r="J99" s="3">
-        <v>0</v>
-      </c>
-      <c r="K99" s="3" t="s">
-        <v>133</v>
+      <c r="J99" s="4">
+        <v>0</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="2">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>45</v>
+        <v>211</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="E100" s="2">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F100" s="2">
         <v>16</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="G100" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I100" s="4">
         <v>0.1</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>133</v>
+      <c r="J100" s="4">
+        <v>0</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="2">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>45</v>
+        <v>212</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="E101" s="2">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F101" s="2">
         <v>16</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="G101" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I101" s="4">
         <v>0.1</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>133</v>
+      <c r="J101" s="4">
+        <v>0</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>47</v>
+        <v>213</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="E102" s="2">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F102" s="2">
         <v>16</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="G102" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I102" s="4">
         <v>0.1</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>133</v>
+      <c r="J102" s="4">
+        <v>0</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="2">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>47</v>
+        <v>214</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="E103" s="2">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F103" s="2">
         <v>16</v>
       </c>
-      <c r="G103" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I103" s="3">
+      <c r="G103" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I103" s="4">
         <v>0.1</v>
       </c>
-      <c r="J103" s="3">
-        <v>0</v>
-      </c>
-      <c r="K103" s="3" t="s">
-        <v>133</v>
+      <c r="J103" s="4">
+        <v>0</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="2">
-        <v>3000</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>85</v>
+        <v>1061</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="E104" s="2">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F104" s="2">
         <v>16</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I104" s="2">
-        <v>1</v>
-      </c>
-      <c r="J104" s="3">
-        <v>0</v>
+      <c r="G104" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I104" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="J104" s="4">
+        <v>0</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -6359,52 +6386,52 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>11</v>

--- a/config/永泰_2_BCU.xlsx
+++ b/config/永泰_2_BCU.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报文" sheetId="1" r:id="rId1"/>
@@ -2173,7 +2173,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2184,13 +2184,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2643,28 +2636,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2673,118 +2669,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -7658,7 +7651,7 @@
         <v>137</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="I47" s="2">
         <v>0.1</v>
